--- a/data/trans_dic/P1417-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1417-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,93</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,22</t>
+          <t>0,0; 3,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,46</t>
+          <t>0,25; 2,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,76; 6,39</t>
+          <t>1,5; 5,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,9</t>
+          <t>1,13; 5,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 11,17</t>
+          <t>2,61; 7,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,25</t>
+          <t>1,04; 3,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,66</t>
+          <t>0,83; 3,45</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 6,81</t>
+          <t>1,65; 4,23</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -867,52 +867,52 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,04</t>
+          <t>0,21; 1,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,97</t>
+          <t>0,17; 2,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,64</t>
+          <t>1,14; 3,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,42</t>
+          <t>0,99; 3,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,08</t>
+          <t>0,21; 2,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 5,67</t>
+          <t>2,64; 5,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,24</t>
+          <t>0,7; 2,2</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,82</t>
+          <t>0,5; 1,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,53</t>
+          <t>0,4; 1,54</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,3</t>
+          <t>1,59; 3,16</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -1002,57 +1002,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,12</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,54</t>
+          <t>0,41; 2,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,27; 2,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,66</t>
+          <t>0,63; 3,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,93</t>
+          <t>0,89; 4,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,08</t>
+          <t>2,17; 5,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,21</t>
+          <t>0,14; 1,19</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,39</t>
+          <t>0,61; 2,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,35</t>
+          <t>0,52; 2,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,29</t>
+          <t>1,59; 3,35</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,32</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1147,52 +1147,52 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,65</t>
+          <t>0,26; 2,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,43</t>
+          <t>0,5; 2,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,65</t>
+          <t>0,47; 2,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,69</t>
+          <t>2,4; 6,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 6,48</t>
+          <t>2,03; 6,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,74</t>
+          <t>2,84; 6,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,53</t>
+          <t>0,26; 1,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,36</t>
+          <t>1,16; 3,38</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,78</t>
+          <t>1,48; 3,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,94</t>
+          <t>2,05; 4,27</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 1,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,66</t>
+          <t>0,46; 4,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 6,23</t>
+          <t>1,08; 6,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 9,53</t>
+          <t>2,72; 9,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,67</t>
+          <t>0,98; 6,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,23</t>
+          <t>1,92; 5,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,6</t>
+          <t>0,74; 3,47</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,75</t>
+          <t>1,88; 5,82</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,22</t>
+          <t>0,7; 3,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,31</t>
+          <t>1,23; 3,09</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -1422,57 +1422,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,48</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,12</t>
+          <t>0,3; 3,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,69</t>
+          <t>2,17; 5,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,95</t>
+          <t>0,36; 2,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,86</t>
+          <t>0,7; 3,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,76</t>
+          <t>0,43; 3,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,87; 8,15</t>
+          <t>3,81; 7,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,5</t>
+          <t>0,18; 1,49</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,65</t>
+          <t>0,54; 2,52</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,67</t>
+          <t>0,6; 2,79</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,23</t>
+          <t>3,42; 6,12</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,51</t>
+          <t>0,15; 1,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,14; 1,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,02</t>
+          <t>1,19; 3,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,1</t>
+          <t>1,33; 3,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,7</t>
+          <t>1,87; 4,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,66</t>
+          <t>1,96; 4,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,09; 9,31</t>
+          <t>7,38; 11,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,44</t>
+          <t>0,91; 2,36</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,55</t>
+          <t>1,06; 2,63</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,63</t>
+          <t>1,13; 2,64</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,68; 5,81</t>
+          <t>4,54; 6,86</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -1702,57 +1702,57 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,39</t>
+          <t>0,14; 1,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,73</t>
+          <t>0,0; 0,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,81</t>
+          <t>0,09; 1,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,67</t>
+          <t>0,92; 2,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,3</t>
+          <t>1,18; 3,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,88</t>
+          <t>1,62; 3,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,35</t>
+          <t>0,83; 2,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,85</t>
+          <t>0,7; 1,83</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,03</t>
+          <t>0,82; 1,96</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,04</t>
+          <t>0,83; 2,07</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,25</t>
+          <t>0,52; 1,47</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,67</t>
+          <t>0,22; 0,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,68</t>
+          <t>0,24; 0,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,87</t>
+          <t>0,36; 0,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,45</t>
+          <t>0,97; 1,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,2</t>
+          <t>1,29; 2,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,34</t>
+          <t>2,22; 3,31</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,04</t>
+          <t>1,95; 3,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,41; 4,94</t>
+          <t>3,93; 5,09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,35</t>
+          <t>0,81; 1,34</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,28; 1,89</t>
+          <t>1,35; 1,98</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,88</t>
+          <t>1,26; 1,85</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,32; 3,09</t>
+          <t>2,6; 3,29</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16052</t>
+          <t>13556</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19194</t>
+          <t>16653</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 8012</t>
+          <t>0; 7969</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5994</t>
+          <t>0; 6822</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 9458</t>
+          <t>0; 9882</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>786; 7663</t>
+          <t>799; 7795</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6381</t>
+          <t>0; 5470</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5053; 18350</t>
+          <t>4320; 16961</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3326; 17024</t>
+          <t>3252; 15905</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8940; 32344</t>
+          <t>8247; 23291</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 9581</t>
+          <t>0; 9084</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5492; 18894</t>
+          <t>6040; 19910</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5223; 21325</t>
+          <t>4857; 20118</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11313; 40908</t>
+          <t>10450; 26837</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3945</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20519</t>
+          <t>20487</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24465</t>
+          <t>24531</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 10494</t>
+          <t>0; 7513</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2427,52 +2427,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1032; 10250</t>
+          <t>1042; 9385</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>919; 10173</t>
+          <t>924; 10600</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5790; 18360</t>
+          <t>5749; 18780</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4977; 17935</t>
+          <t>5180; 17890</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1085; 10900</t>
+          <t>1094; 10916</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13815; 29110</t>
+          <t>14353; 29030</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6821; 22286</t>
+          <t>6999; 21917</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5222; 18752</t>
+          <t>5133; 18862</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4062; 15703</t>
+          <t>4089; 15830</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16423; 33944</t>
+          <t>17107; 33941</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11663</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15290</t>
+          <t>15660</t>
         </is>
       </c>
     </row>
@@ -2630,57 +2630,57 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6871</t>
+          <t>0; 6354</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3960</t>
+          <t>0; 5081</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1280; 8016</t>
+          <t>1290; 7263</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 7700</t>
+          <t>905; 7821</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2168; 12494</t>
+          <t>2148; 12496</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2817; 13212</t>
+          <t>2992; 13828</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7321; 17721</t>
+          <t>7741; 18405</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>910; 7906</t>
+          <t>911; 7760</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4074; 15913</t>
+          <t>4041; 15497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3639; 15399</t>
+          <t>3405; 14439</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9754; 21898</t>
+          <t>10683; 22517</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>4752</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17017</t>
+          <t>18638</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20933</t>
+          <t>23391</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4736</t>
+          <t>0; 5334</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2843,52 +2843,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1035; 9791</t>
+          <t>974; 8934</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1680; 7605</t>
+          <t>1878; 9588</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1809; 9859</t>
+          <t>1737; 10475</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9852; 26028</t>
+          <t>9335; 26548</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8339; 25100</t>
+          <t>7873; 24078</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9975; 27288</t>
+          <t>11992; 27715</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1884; 11153</t>
+          <t>1897; 11876</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9145; 25642</t>
+          <t>8846; 25801</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12087; 28600</t>
+          <t>11234; 28929</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13458; 31078</t>
+          <t>16283; 33937</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7966</t>
+          <t>8473</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3758</t>
+          <t>0; 3296</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>986; 9912</t>
+          <t>975; 8587</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5361</t>
+          <t>0; 4884</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3603</t>
+          <t>0; 3173</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2160; 12930</t>
+          <t>2246; 12915</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6017; 20929</t>
+          <t>5971; 21020</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2222; 12402</t>
+          <t>2139; 13562</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4231; 10876</t>
+          <t>4340; 11780</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3044; 14784</t>
+          <t>3024; 14275</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8935; 24870</t>
+          <t>8111; 25169</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3019; 13832</t>
+          <t>3024; 13422</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5104; 12812</t>
+          <t>5334; 13367</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9799</t>
+          <t>9702</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>14501</t>
+          <t>14423</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>24300</t>
+          <t>24125</t>
         </is>
       </c>
     </row>
@@ -3254,57 +3254,57 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6786</t>
+          <t>0; 7028</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>802; 8197</t>
+          <t>790; 8504</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6120; 15334</t>
+          <t>5880; 15149</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1013; 8201</t>
+          <t>1014; 8278</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1929; 10747</t>
+          <t>1941; 10769</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1200; 10261</t>
+          <t>1184; 10044</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9929; 20898</t>
+          <t>10024; 20829</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1008; 8234</t>
+          <t>1003; 8193</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2947; 14629</t>
+          <t>2964; 13895</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2893; 14337</t>
+          <t>3229; 14957</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18091; 32748</t>
+          <t>18265; 32669</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10809</t>
+          <t>14677</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>56083</t>
+          <t>70091</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>66892</t>
+          <t>84768</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>931; 9277</t>
+          <t>943; 8382</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 6521</t>
+          <t>0; 7022</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 7233</t>
+          <t>886; 7176</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6021; 18747</t>
+          <t>8553; 24638</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9424; 26186</t>
+          <t>8474; 25212</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12188; 32607</t>
+          <t>13005; 33883</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13495; 32244</t>
+          <t>13518; 31624</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>26212; 78940</t>
+          <t>56824; 87394</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11505; 30611</t>
+          <t>11344; 29537</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13450; 34612</t>
+          <t>14430; 35733</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15425; 35402</t>
+          <t>15215; 35588</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>39341; 85352</t>
+          <t>67516; 101985</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2519</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>10278</t>
+          <t>11809</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>12797</t>
+          <t>14636</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1808; 10572</t>
+          <t>1819; 10571</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1097; 10823</t>
+          <t>1060; 10616</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 5662</t>
+          <t>0; 5176</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>359; 7512</t>
+          <t>740; 8136</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7375; 20892</t>
+          <t>7180; 21533</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10189; 27077</t>
+          <t>9673; 26309</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13476; 32055</t>
+          <t>13381; 32143</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5718; 16808</t>
+          <t>6894; 20541</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>10765; 28251</t>
+          <t>10651; 27897</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13569; 32553</t>
+          <t>13055; 31433</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>13612; 32811</t>
+          <t>13348; 33214</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>6510; 20618</t>
+          <t>8422; 23859</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>38763</t>
+          <t>43753</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>153074</t>
+          <t>168484</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>191837</t>
+          <t>212236</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>7344; 22078</t>
+          <t>7324; 22343</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9030; 23462</t>
+          <t>8302; 24472</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12136; 29576</t>
+          <t>12062; 30491</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26685; 50183</t>
+          <t>34099; 57097</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>43609; 74177</t>
+          <t>43731; 75000</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>77799; 118642</t>
+          <t>78955; 117794</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>70214; 107871</t>
+          <t>68985; 106283</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>124627; 180486</t>
+          <t>146499; 189643</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>54087; 89947</t>
+          <t>54059; 89366</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>89615; 132235</t>
+          <t>94271; 137955</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>87871; 130168</t>
+          <t>87288; 128433</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>165015; 219937</t>
+          <t>189004; 238462</t>
         </is>
       </c>
     </row>
